--- a/ZonasEscolares/excels/ICA-CHINCHA-PUEBLO_NUEVO.xlsx
+++ b/ZonasEscolares/excels/ICA-CHINCHA-PUEBLO_NUEVO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PUEBLO_NUEVO</t>
+          <t>PUEBLO NUEVO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/ICA-CHINCHA-PUEBLO_NUEVO.xlsx
+++ b/ZonasEscolares/excels/ICA-CHINCHA-PUEBLO_NUEVO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>411</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-13.390821</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.147848</v>
-      </c>
-      <c r="I2" t="n">
-        <v>72</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-13.390821</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.147848</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>22683</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-13.389539</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.14797299999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>164</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-13.389539</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.147973</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>HORACIO ZEBALLOS GAMEZ</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-13.405009</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.12111</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1063</v>
-      </c>
-      <c r="J4" t="n">
-        <v>56</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-13.405009</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.12111</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>DOS DE MAYO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-13.403989</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.13350199999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>863</v>
-      </c>
-      <c r="J5" t="n">
-        <v>42</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-13.403989</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.133502</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>JOSE YATACO PACHAS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-13.407022</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.13199899999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>777</v>
-      </c>
-      <c r="J6" t="n">
-        <v>38</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-13.407022</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.131999</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>22255 ROLANDO ALZAMORA PAREDES</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-13.40072</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.12466000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>254</v>
-      </c>
-      <c r="J7" t="n">
-        <v>12</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-13.40072</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.12466</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>22480 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-13.401059</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.13301300000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>460</v>
-      </c>
-      <c r="J8" t="n">
-        <v>19</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-13.401059</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.133013</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>22687 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-13.3992</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.1442</v>
-      </c>
-      <c r="I9" t="n">
-        <v>429</v>
-      </c>
-      <c r="J9" t="n">
-        <v>22</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-13.3992</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.1442</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>252</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-13.40066</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.11951999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>211</v>
-      </c>
-      <c r="J10" t="n">
-        <v>11</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-13.40066</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.11952</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>22774</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-13.39326</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.144994</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1212</v>
-      </c>
-      <c r="J11" t="n">
-        <v>53</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-13.39326</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.144994</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>9 DE DICIEMBRE</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-13.399799</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.132527</v>
-      </c>
-      <c r="I12" t="n">
-        <v>557</v>
-      </c>
-      <c r="J12" t="n">
-        <v>33</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-13.399799</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.132527</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>FE Y ALEGRIA 30</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-13.395509</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.139779</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1150</v>
-      </c>
-      <c r="J13" t="n">
-        <v>52</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-13.395509</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.139779</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>PITAGORAS</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-13.40095</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.13817</v>
-      </c>
-      <c r="I14" t="n">
-        <v>479</v>
-      </c>
-      <c r="J14" t="n">
-        <v>23</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-13.40095</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.13817</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>PRISMA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-13.39806</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.12226</v>
-      </c>
-      <c r="I15" t="n">
-        <v>323</v>
-      </c>
-      <c r="J15" t="n">
-        <v>19</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-13.39806</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.12226</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>CAYROS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-13.39243</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.15137</v>
-      </c>
-      <c r="I16" t="n">
-        <v>566</v>
-      </c>
-      <c r="J16" t="n">
-        <v>25</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-13.39243</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.15137</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>306</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-13.391121</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.108934</v>
-      </c>
-      <c r="I17" t="n">
-        <v>290</v>
-      </c>
-      <c r="J17" t="n">
-        <v>10</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-13.391121</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.108934</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>GEORGE WASHINGTON CARVER</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-13.38955</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.14717</v>
-      </c>
-      <c r="I18" t="n">
-        <v>175</v>
-      </c>
-      <c r="J18" t="n">
-        <v>17</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-13.38955</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.14717</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>PITAGORAS SCHOOL</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-13.40362</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.12882</v>
-      </c>
-      <c r="I19" t="n">
-        <v>325</v>
-      </c>
-      <c r="J19" t="n">
-        <v>24</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-13.40362</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.12882</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/ICA-CHINCHA-PUEBLO_NUEVO.xlsx
+++ b/ZonasEscolares/excels/ICA-CHINCHA-PUEBLO_NUEVO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>215595</t>
+          <t>591677</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>306</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.390821</t>
+          <t>-13.391121</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.147848</t>
+          <t>-76.108934</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>215703</t>
+          <t>215840</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.389539</t>
+          <t>-13.40066</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.147973</t>
+          <t>-76.11952</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>215736</t>
+          <t>215760</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HORACIO ZEBALLOS GAMEZ</t>
+          <t>22255 ROLANDO ALZAMORA PAREDES</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.405009</t>
+          <t>-13.40072</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.12111</t>
+          <t>-76.12466</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>215741</t>
+          <t>637802</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DOS DE MAYO</t>
+          <t>GEORGE WASHINGTON CARVER</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.403989</t>
+          <t>-13.38955</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.133502</t>
+          <t>-76.14717</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>215755</t>
+          <t>215784</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JOSE YATACO PACHAS</t>
+          <t>22480 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.407022</t>
+          <t>-13.401059</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.131999</t>
+          <t>-76.133013</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>460</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>215760</t>
+          <t>578355</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22255 ROLANDO ALZAMORA PAREDES</t>
+          <t>PRISMA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.40072</t>
+          <t>-13.39806</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.12466</t>
+          <t>-76.12226</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>323</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>215784</t>
+          <t>215802</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22480 JOSE CARLOS MARIATEGUI</t>
+          <t>22687 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.401059</t>
+          <t>-13.3992</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.133013</t>
+          <t>-76.1442</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>429</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>215802</t>
+          <t>518521</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22687 ALMIRANTE MIGUEL GRAU</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.3992</t>
+          <t>-13.40095</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.1442</t>
+          <t>-76.13817</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>479</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>215840</t>
+          <t>638260</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>PITAGORAS SCHOOL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.40066</t>
+          <t>-13.40362</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.11952</t>
+          <t>-76.12882</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>215864</t>
+          <t>591248</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22774</t>
+          <t>CAYROS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.39326</t>
+          <t>-13.39243</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.144994</t>
+          <t>-76.15137</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>566</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>215897</t>
+          <t>215595</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9 DE DICIEMBRE</t>
+          <t>411</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.399799</t>
+          <t>-13.390821</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.132527</t>
+          <t>-76.147848</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>215944</t>
+          <t>215897</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 30</t>
+          <t>9 DE DICIEMBRE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.395509</t>
+          <t>-13.399799</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.139779</t>
+          <t>-76.132527</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>557</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>518521</t>
+          <t>215755</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>JOSE YATACO PACHAS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.40095</t>
+          <t>-13.407022</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.13817</t>
+          <t>-76.131999</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>777</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>578355</t>
+          <t>215741</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PRISMA</t>
+          <t>DOS DE MAYO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.39806</t>
+          <t>-13.403989</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.12226</t>
+          <t>-76.133502</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>863</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>591248</t>
+          <t>215944</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CAYROS</t>
+          <t>FE Y ALEGRIA 30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.39243</t>
+          <t>-13.395509</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.15137</t>
+          <t>-76.139779</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>591677</t>
+          <t>215864</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>22774</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.391121</t>
+          <t>-13.39326</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.108934</t>
+          <t>-76.144994</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>637802</t>
+          <t>215736</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GEORGE WASHINGTON CARVER</t>
+          <t>HORACIO ZEBALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.38955</t>
+          <t>-13.405009</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.14717</t>
+          <t>-76.12111</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>638260</t>
+          <t>215703</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PITAGORAS SCHOOL</t>
+          <t>22683</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.40362</t>
+          <t>-13.389539</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.12882</t>
+          <t>-76.147973</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>164</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">

--- a/ZonasEscolares/excels/ICA-CHINCHA-PUEBLO_NUEVO.xlsx
+++ b/ZonasEscolares/excels/ICA-CHINCHA-PUEBLO_NUEVO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>591677</t>
+          <t>638260</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>PITAGORAS SCHOOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.391121</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.108934</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-13.40362</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.12882</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>215840</t>
+          <t>637802</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>GEORGE WASHINGTON CARVER</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.40066</t>
+          <t>175</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.11952</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-13.38955</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.14717</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>215760</t>
+          <t>591677</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22255 ROLANDO ALZAMORA PAREDES</t>
+          <t>306</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.40072</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.12466</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-13.391121</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.108934</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>637802</t>
+          <t>591248</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GEORGE WASHINGTON CARVER</t>
+          <t>CAYROS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.38955</t>
+          <t>566</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.14717</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>-13.39243</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.15137</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>215784</t>
+          <t>578355</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22480 JOSE CARLOS MARIATEGUI</t>
+          <t>PRISMA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.401059</t>
+          <t>323</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.133013</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>-13.39806</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.12226</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>578355</t>
+          <t>518521</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PRISMA</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.39806</t>
+          <t>479</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.12226</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>-13.40095</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.13817</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>215802</t>
+          <t>215944</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22687 ALMIRANTE MIGUEL GRAU</t>
+          <t>FE Y ALEGRIA 30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.3992</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.1442</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>-13.395509</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.139779</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>518521</t>
+          <t>215897</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>9 DE DICIEMBRE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.40095</t>
+          <t>557</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.13817</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>-13.399799</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.132527</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>638260</t>
+          <t>215864</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PITAGORAS SCHOOL</t>
+          <t>22774</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.40362</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.12882</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>-13.39326</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.144994</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>591248</t>
+          <t>215840</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CAYROS</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.39243</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.15137</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>-13.40066</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.11952</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>215595</t>
+          <t>215802</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>22687 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.390821</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.147848</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-13.3992</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.1442</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>215897</t>
+          <t>215784</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>9 DE DICIEMBRE</t>
+          <t>22480 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.399799</t>
+          <t>460</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.132527</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>-13.401059</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.133013</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>215755</t>
+          <t>215760</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JOSE YATACO PACHAS</t>
+          <t>22255 ROLANDO ALZAMORA PAREDES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.407022</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.131999</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>-13.40072</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.12466</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>215741</t>
+          <t>215755</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DOS DE MAYO</t>
+          <t>JOSE YATACO PACHAS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.403989</t>
+          <t>777</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.133502</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>-13.407022</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-76.131999</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>215944</t>
+          <t>215741</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 30</t>
+          <t>DOS DE MAYO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.395509</t>
+          <t>863</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.139779</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>-13.403989</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-76.133502</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>215864</t>
+          <t>215736</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22774</t>
+          <t>HORACIO ZEBALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.39326</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.144994</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>-13.405009</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-76.12111</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>215736</t>
+          <t>215703</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>HORACIO ZEBALLOS GAMEZ</t>
+          <t>22683</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.405009</t>
+          <t>164</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.12111</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>-13.389539</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-76.147973</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>215703</t>
+          <t>215595</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>411</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.389539</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.147973</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>-13.390821</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-76.147848</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">

--- a/ZonasEscolares/excels/ICA-CHINCHA-PUEBLO_NUEVO.xlsx
+++ b/ZonasEscolares/excels/ICA-CHINCHA-PUEBLO_NUEVO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
